--- a/data/trans_orig/P36B08-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B08-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de verduras, ensaladas y hortalizas en 2007</t>
+          <t>Población según la frecuencia de consumo de verduras, ensaladas y hortalizas en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>10570</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12367</t>
+          <t>11407</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23743</t>
+          <t>24335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15466</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>14524</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33220</t>
+          <t>33684</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103088</t>
+          <t>103046</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>141539</t>
+          <t>143029</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>56138</t>
+          <t>55834</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85063</t>
+          <t>85981</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>167295</t>
+          <t>169387</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>215981</t>
+          <t>217757</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>180663</t>
+          <t>181512</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>224714</t>
+          <t>223774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>104176</t>
+          <t>104609</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>139559</t>
+          <t>139989</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>297009</t>
+          <t>300258</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>352177</t>
+          <t>355085</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,55%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111173</t>
+          <t>112083</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149269</t>
+          <t>149468</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89952</t>
+          <t>90079</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>124491</t>
+          <t>122465</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>209880</t>
+          <t>208083</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>262508</t>
+          <t>260243</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>888</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>11433</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17048</t>
+          <t>16938</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14837</t>
+          <t>14184</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34660</t>
+          <t>34017</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19872</t>
+          <t>20323</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26004</t>
+          <t>24161</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>48851</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85655</t>
+          <t>87884</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>121081</t>
+          <t>121941</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>82916</t>
+          <t>81462</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>117798</t>
+          <t>114606</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>178479</t>
+          <t>178386</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>228912</t>
+          <t>226953</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>142399</t>
+          <t>142870</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>182926</t>
+          <t>182360</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>131538</t>
+          <t>130060</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>168043</t>
+          <t>167812</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>286123</t>
+          <t>287035</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>339041</t>
+          <t>341008</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,16%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59303</t>
+          <t>59346</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90859</t>
+          <t>91397</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89742</t>
+          <t>90491</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126029</t>
+          <t>124794</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>160367</t>
+          <t>157750</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>206870</t>
+          <t>204908</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17948</t>
+          <t>18550</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14487</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27707</t>
+          <t>26687</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34239</t>
+          <t>34892</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61667</t>
+          <t>62335</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>10085</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38453</t>
+          <t>38528</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66237</t>
+          <t>65307</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>127757</t>
+          <t>127938</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>169437</t>
+          <t>169694</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29457</t>
+          <t>29267</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52176</t>
+          <t>51810</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>163721</t>
+          <t>165434</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>211945</t>
+          <t>211829</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>186136</t>
+          <t>188121</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>231496</t>
+          <t>233431</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49019</t>
+          <t>49422</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72853</t>
+          <t>73067</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>243607</t>
+          <t>244275</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>297465</t>
+          <t>295062</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>108934</t>
+          <t>110259</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>150438</t>
+          <t>150156</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44895</t>
+          <t>43371</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68977</t>
+          <t>67992</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>160613</t>
+          <t>162214</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>210040</t>
+          <t>208408</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20735</t>
+          <t>20443</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41618</t>
+          <t>42102</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20564</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30627</t>
+          <t>29353</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56101</t>
+          <t>54896</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>61948</t>
+          <t>62481</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>96960</t>
+          <t>99472</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26992</t>
+          <t>26767</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>51155</t>
+          <t>50308</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>95565</t>
+          <t>97485</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>137638</t>
+          <t>138254</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>298900</t>
+          <t>294394</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>362104</t>
+          <t>359165</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>137117</t>
+          <t>136330</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>178936</t>
+          <t>180571</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>449596</t>
+          <t>448595</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>526481</t>
+          <t>522983</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>497415</t>
+          <t>499503</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>568665</t>
+          <t>569578</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>276650</t>
+          <t>279023</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>329928</t>
+          <t>330425</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>795699</t>
+          <t>795016</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>881631</t>
+          <t>885168</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,33%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>238193</t>
+          <t>236695</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>296492</t>
+          <t>296691</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>180740</t>
+          <t>180868</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>229603</t>
+          <t>227853</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>432173</t>
+          <t>429361</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>510600</t>
+          <t>504442</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19643</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,47 +3475,47 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>9225</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>4697</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>17181</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>9225</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>4116</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>16666</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>11595</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>29939</t>
+          <t>29452</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21871</t>
+          <t>22678</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>44644</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14001</t>
+          <t>15137</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34946</t>
+          <t>34532</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>43253</t>
+          <t>41864</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>73236</t>
+          <t>71580</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>84877</t>
+          <t>83937</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>119935</t>
+          <t>120060</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>115434</t>
+          <t>112273</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>155822</t>
+          <t>154274</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>207161</t>
+          <t>210261</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>260113</t>
+          <t>261878</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>130350</t>
+          <t>131141</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>167319</t>
+          <t>170334</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>235978</t>
+          <t>238943</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>284244</t>
+          <t>288288</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>379388</t>
+          <t>381339</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>438564</t>
+          <t>440089</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,93%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>43739</t>
+          <t>44793</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>71798</t>
+          <t>72180</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>121333</t>
+          <t>121366</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>164023</t>
+          <t>163636</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>174431</t>
+          <t>173644</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>226402</t>
+          <t>223935</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21837</t>
+          <t>23335</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13982</t>
+          <t>14341</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14386</t>
+          <t>13541</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>33078</t>
+          <t>32063</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>21854</t>
+          <t>22556</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>43208</t>
+          <t>43428</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>47515</t>
+          <t>46879</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>77554</t>
+          <t>77269</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>74938</t>
+          <t>75722</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>111063</t>
+          <t>112962</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>81386</t>
+          <t>81613</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>113832</t>
+          <t>113933</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>261621</t>
+          <t>261037</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>321025</t>
+          <t>320342</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>352193</t>
+          <t>355961</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>423251</t>
+          <t>422446</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>105847</t>
+          <t>107447</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>138749</t>
+          <t>140955</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>530584</t>
+          <t>530891</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>601394</t>
+          <t>599208</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>647306</t>
+          <t>647789</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>728831</t>
+          <t>724517</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,83%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>21475</t>
+          <t>21866</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>42825</t>
+          <t>44428</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>296564</t>
+          <t>296712</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>356080</t>
+          <t>357273</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>323948</t>
+          <t>324465</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>390809</t>
+          <t>389847</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>57274</t>
+          <t>58165</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>91620</t>
+          <t>91993</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>30417</t>
+          <t>29997</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>57679</t>
+          <t>55276</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>95305</t>
+          <t>95105</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>138508</t>
+          <t>137702</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>200199</t>
+          <t>202300</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>258111</t>
+          <t>261085</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>122691</t>
+          <t>124338</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>170362</t>
+          <t>172156</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>338313</t>
+          <t>335677</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>411726</t>
+          <t>413554</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>850710</t>
+          <t>848648</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>956333</t>
+          <t>952196</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>743371</t>
+          <t>739305</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>837045</t>
+          <t>836190</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1620897</t>
+          <t>1621046</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1772933</t>
+          <t>1759622</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,47%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1325415</t>
+          <t>1327232</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1435914</t>
+          <t>1441638</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1399569</t>
+          <t>1407284</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1520128</t>
+          <t>1514268</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2753563</t>
+          <t>2763458</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2921337</t>
+          <t>2920548</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>637892</t>
+          <t>641010</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>732765</t>
+          <t>737085</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>890479</t>
+          <t>887395</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>993479</t>
+          <t>991698</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1554754</t>
+          <t>1557709</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1699104</t>
+          <t>1693626</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de verduras, ensaladas y hortalizas en 2012</t>
+          <t>Población según la frecuencia de consumo de verduras, ensaladas y hortalizas en 2012 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15785</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7807</t>
+          <t>6559</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18183</t>
+          <t>19352</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>7893</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22959</t>
+          <t>23971</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9758</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28530</t>
+          <t>27012</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60622</t>
+          <t>61965</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94956</t>
+          <t>96015</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24483</t>
+          <t>24080</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48336</t>
+          <t>47817</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91224</t>
+          <t>92858</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>133379</t>
+          <t>133410</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>135363</t>
+          <t>136134</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>176347</t>
+          <t>177934</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88987</t>
+          <t>87647</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123784</t>
+          <t>124019</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>230852</t>
+          <t>233384</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>288629</t>
+          <t>290158</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160565</t>
+          <t>160614</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>203097</t>
+          <t>203068</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>149785</t>
+          <t>149762</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>185914</t>
+          <t>187170</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>322607</t>
+          <t>320532</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>377589</t>
+          <t>376855</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,41%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>852</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7389</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11876</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14900</t>
+          <t>13488</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5996</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18786</t>
+          <t>18565</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,82 +6550,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>7069</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2959</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>14401</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>17803</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>10850</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>27357</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>1,44%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>7069</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3043</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>14002</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>17803</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>10935</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>28137</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72530</t>
+          <t>73705</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>108601</t>
+          <t>109195</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47397</t>
+          <t>45566</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75437</t>
+          <t>76140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>128732</t>
+          <t>127729</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>176678</t>
+          <t>176123</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>138622</t>
+          <t>143515</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>183455</t>
+          <t>185474</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81560</t>
+          <t>80398</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115457</t>
+          <t>115307</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>232608</t>
+          <t>231505</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>288821</t>
+          <t>288816</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>130977</t>
+          <t>130480</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>174772</t>
+          <t>172539</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>147463</t>
+          <t>148036</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>185962</t>
+          <t>187685</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>289188</t>
+          <t>290473</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>347877</t>
+          <t>347615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11971</t>
+          <t>12377</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,82 +7119,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>904</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4936</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>6585</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2780</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>13191</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>904</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4606</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>6585</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>2863</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>13809</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14349</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33701</t>
+          <t>34097</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,82 +7232,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>11308</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5362</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>20451</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>34139</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>23766</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>47590</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>5,35%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>11308</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>5314</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>20692</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>34139</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>24686</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>48396</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>112985</t>
+          <t>112802</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>158103</t>
+          <t>155867</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27578</t>
+          <t>26338</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49540</t>
+          <t>50584</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>147303</t>
+          <t>146946</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>197490</t>
+          <t>194848</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>205538</t>
+          <t>207841</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>256880</t>
+          <t>257685</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66613</t>
+          <t>66082</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96804</t>
+          <t>96389</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>284054</t>
+          <t>282434</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>337684</t>
+          <t>341143</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212764</t>
+          <t>213116</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263002</t>
+          <t>261882</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>114445</t>
+          <t>113540</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>146538</t>
+          <t>146820</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>337824</t>
+          <t>336150</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>396010</t>
+          <t>396019</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>11211</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28083</t>
+          <t>29582</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19501</t>
+          <t>18034</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19495</t>
+          <t>19280</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40895</t>
+          <t>40453</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>35855</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63458</t>
+          <t>63465</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15522</t>
+          <t>15743</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>36088</t>
+          <t>37687</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>54485</t>
+          <t>54844</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>89855</t>
+          <t>89145</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>243757</t>
+          <t>241754</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>303194</t>
+          <t>301277</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>111467</t>
+          <t>109708</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>154672</t>
+          <t>156604</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>366755</t>
+          <t>364648</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>441056</t>
+          <t>438035</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>371206</t>
+          <t>372527</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>444180</t>
+          <t>441313</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>232260</t>
+          <t>230427</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>284316</t>
+          <t>287187</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>623267</t>
+          <t>624520</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>708397</t>
+          <t>711378</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>377638</t>
+          <t>378961</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>445846</t>
+          <t>446606</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>312186</t>
+          <t>310703</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>367343</t>
+          <t>369431</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>703800</t>
+          <t>704470</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>792812</t>
+          <t>795993</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,48%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17373</t>
+          <t>17497</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15918</t>
+          <t>15455</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10763</t>
+          <t>11149</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>28108</t>
+          <t>27374</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16600</t>
+          <t>17051</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38013</t>
+          <t>38526</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15343</t>
+          <t>15138</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34653</t>
+          <t>35004</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>37671</t>
+          <t>36341</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>64615</t>
+          <t>64435</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>96885</t>
+          <t>96203</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>136766</t>
+          <t>134287</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>108422</t>
+          <t>109227</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>152486</t>
+          <t>152338</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>219284</t>
+          <t>218559</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>276255</t>
+          <t>274580</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>148193</t>
+          <t>147766</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>190439</t>
+          <t>189989</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>222917</t>
+          <t>223345</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>275728</t>
+          <t>275032</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>384562</t>
+          <t>383766</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>451040</t>
+          <t>450282</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>169839</t>
+          <t>169624</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>212426</t>
+          <t>214880</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>319997</t>
+          <t>321615</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>376324</t>
+          <t>380281</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>504767</t>
+          <t>503575</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>575454</t>
+          <t>574278</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,22%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>20159</t>
+          <t>20758</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>20265</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16285</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>37921</t>
+          <t>36382</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>19240</t>
+          <t>18201</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>38005</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>24194</t>
+          <t>24112</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>48674</t>
+          <t>48922</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>47301</t>
+          <t>47241</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>78209</t>
+          <t>78134</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>77928</t>
+          <t>77466</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>107943</t>
+          <t>108874</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>164569</t>
+          <t>163386</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>213551</t>
+          <t>216770</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>253984</t>
+          <t>251717</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>314491</t>
+          <t>311238</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>64356</t>
+          <t>63304</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>94456</t>
+          <t>93020</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>357807</t>
+          <t>356512</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>423348</t>
+          <t>424080</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>434849</t>
+          <t>434637</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>504500</t>
+          <t>502080</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>42989</t>
+          <t>43322</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>69716</t>
+          <t>70597</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>453463</t>
+          <t>450439</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>516686</t>
+          <t>519043</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>503120</t>
+          <t>504050</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>575853</t>
+          <t>575539</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>42325</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>74555</t>
+          <t>72327</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>26368</t>
+          <t>25179</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>50096</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>74210</t>
+          <t>74974</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>112391</t>
+          <t>114150</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>124334</t>
+          <t>124683</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>174115</t>
+          <t>173559</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>85697</t>
+          <t>85424</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>128015</t>
+          <t>127048</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,47 +9995,47 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>251726</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>222452</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>283706</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
           <t>3,62%</t>
         </is>
       </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>251726</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>217529</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>283163</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>731804</t>
+          <t>730206</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>831740</t>
+          <t>832877</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>539742</t>
+          <t>541235</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>628461</t>
+          <t>626707</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1298251</t>
+          <t>1297076</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1430267</t>
+          <t>1434294</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1152057</t>
+          <t>1150584</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1263190</t>
+          <t>1261568</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1121436</t>
+          <t>1127615</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1242488</t>
+          <t>1241456</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2304270</t>
+          <t>2302222</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2459839</t>
+          <t>2469359</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,5%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1168470</t>
+          <t>1172304</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1285692</t>
+          <t>1283491</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1577641</t>
+          <t>1571191</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1704243</t>
+          <t>1694108</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2779503</t>
+          <t>2778916</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2948431</t>
+          <t>2947352</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,38%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de verduras, ensaladas y hortalizas en 2016</t>
+          <t>Población según la frecuencia de consumo de verduras, ensaladas y hortalizas en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10768,7 +10768,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>8502</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11032</t>
+          <t>12069</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21936</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>15252</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11585</t>
+          <t>11752</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31128</t>
+          <t>31212</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60256</t>
+          <t>62178</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94295</t>
+          <t>96720</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38737</t>
+          <t>39264</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>66648</t>
+          <t>65241</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>108095</t>
+          <t>109939</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>150662</t>
+          <t>152828</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>164890</t>
+          <t>164931</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>206956</t>
+          <t>208982</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>126232</t>
+          <t>125011</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>160860</t>
+          <t>162061</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>299186</t>
+          <t>300314</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>358814</t>
+          <t>358010</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>133318</t>
+          <t>133661</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>173083</t>
+          <t>176665</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>122411</t>
+          <t>122536</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>160322</t>
+          <t>158411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>265494</t>
+          <t>265955</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>321950</t>
+          <t>322154</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,56%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>997</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t>9885</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,82 +11445,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2219</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7060</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>6158</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>12815</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2219</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7613</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>6158</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>2233</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>13091</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21997</t>
+          <t>23178</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17372</t>
+          <t>16955</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14238</t>
+          <t>14341</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33135</t>
+          <t>33254</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48921</t>
+          <t>49740</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>80107</t>
+          <t>80245</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52074</t>
+          <t>50579</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83040</t>
+          <t>80376</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>107442</t>
+          <t>109510</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>149643</t>
+          <t>150018</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>159706</t>
+          <t>160839</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>200241</t>
+          <t>200692</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>138361</t>
+          <t>138973</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178425</t>
+          <t>175356</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>309387</t>
+          <t>310632</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>365573</t>
+          <t>367381</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96891</t>
+          <t>97778</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>134338</t>
+          <t>135042</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113763</t>
+          <t>114574</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>150134</t>
+          <t>151271</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>222096</t>
+          <t>225103</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>274937</t>
+          <t>274964</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16530</t>
+          <t>15122</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17940</t>
+          <t>18485</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17946</t>
+          <t>18065</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39335</t>
+          <t>39318</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18678</t>
+          <t>18829</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41391</t>
+          <t>41177</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>103203</t>
+          <t>102482</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>144945</t>
+          <t>144618</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>19376</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41078</t>
+          <t>40488</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>130821</t>
+          <t>128362</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>173876</t>
+          <t>172777</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>208812</t>
+          <t>206437</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>252059</t>
+          <t>254003</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57400</t>
+          <t>58294</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84177</t>
+          <t>84219</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>276734</t>
+          <t>276396</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>329340</t>
+          <t>331384</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>112581</t>
+          <t>115762</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>152420</t>
+          <t>156242</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48013</t>
+          <t>48374</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>74142</t>
+          <t>73895</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>168320</t>
+          <t>170069</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>218037</t>
+          <t>216802</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12935</t>
+          <t>13726</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6775</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20682</t>
+          <t>21434</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11962</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29818</t>
+          <t>28571</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36213</t>
+          <t>35670</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>64022</t>
+          <t>63836</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>9667</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26206</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>49456</t>
+          <t>50456</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83648</t>
+          <t>82240</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>247249</t>
+          <t>246294</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>304394</t>
+          <t>304122</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>146541</t>
+          <t>146974</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>192906</t>
+          <t>193897</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>406859</t>
+          <t>409768</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>481834</t>
+          <t>487055</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>479707</t>
+          <t>480873</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>548976</t>
+          <t>547325</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>314759</t>
+          <t>315422</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>374797</t>
+          <t>373140</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>812513</t>
+          <t>809109</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>902427</t>
+          <t>903426</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,03%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>263663</t>
+          <t>267195</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>321790</t>
+          <t>324674</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>254515</t>
+          <t>253276</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>312224</t>
+          <t>308256</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>539440</t>
+          <t>537561</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>620215</t>
+          <t>619298</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17319</t>
+          <t>16665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16796</t>
+          <t>16253</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11536</t>
+          <t>11647</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>28600</t>
+          <t>29617</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>14166</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>33008</t>
+          <t>32817</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>26930</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27834</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>52296</t>
+          <t>50777</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>117734</t>
+          <t>117684</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>158451</t>
+          <t>160659</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>115742</t>
+          <t>115974</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>157212</t>
+          <t>158524</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>242638</t>
+          <t>247192</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>302667</t>
+          <t>306308</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>257527</t>
+          <t>258159</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>307767</t>
+          <t>308468</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>293930</t>
+          <t>295223</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>351915</t>
+          <t>346937</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>570028</t>
+          <t>567816</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>640309</t>
+          <t>641565</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,43%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>143541</t>
+          <t>141870</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>186997</t>
+          <t>188941</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>228173</t>
+          <t>224761</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>280894</t>
+          <t>278731</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>383253</t>
+          <t>384413</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>450961</t>
+          <t>453761</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,54%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15719</t>
+          <t>14819</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8640</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25182</t>
+          <t>25096</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>14585</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>34697</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9538</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26038</t>
+          <t>25866</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>25926</t>
+          <t>26271</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>51314</t>
+          <t>51438</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>40728</t>
+          <t>41272</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>69818</t>
+          <t>69862</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,7 +14356,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>69065</t>
+          <t>66147</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>100752</t>
+          <t>98718</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>183082</t>
+          <t>182144</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>239619</t>
+          <t>236144</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>263943</t>
+          <t>263279</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>322565</t>
+          <t>323944</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>92651</t>
+          <t>92287</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>125267</t>
+          <t>125679</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>406500</t>
+          <t>404562</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>468485</t>
+          <t>471916</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>507895</t>
+          <t>509688</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>581598</t>
+          <t>585764</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,01%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>55926</t>
+          <t>55913</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>85830</t>
+          <t>85086</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>345485</t>
+          <t>343924</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>407467</t>
+          <t>411232</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>410795</t>
+          <t>413289</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>486687</t>
+          <t>480976</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,32%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>26797</t>
+          <t>27484</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>52144</t>
+          <t>52234</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>31574</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>57974</t>
+          <t>58932</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>65735</t>
+          <t>62957</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>100970</t>
+          <t>98917</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>114234</t>
+          <t>116245</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>160511</t>
+          <t>164106</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>71199</t>
+          <t>73274</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>108830</t>
+          <t>110951</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>200128</t>
+          <t>196844</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>260905</t>
+          <t>258944</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>709748</t>
+          <t>705595</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>807536</t>
+          <t>807521</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>614602</t>
+          <t>613329</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>706441</t>
+          <t>709315</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1353399</t>
+          <t>1354471</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1496736</t>
+          <t>1488382</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1451456</t>
+          <t>1449445</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1567875</t>
+          <t>1561123</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1418202</t>
+          <t>1416808</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1539012</t>
+          <t>1537844</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2892337</t>
+          <t>2894697</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3056659</t>
+          <t>3065764</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,54%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>881514</t>
+          <t>878832</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>991723</t>
+          <t>984555</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1187410</t>
+          <t>1188117</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1304452</t>
+          <t>1305355</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2103032</t>
+          <t>2092005</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2260192</t>
+          <t>2253460</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B08-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B08-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10570</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24335</t>
+          <t>23458</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>14719</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14524</t>
+          <t>14541</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33684</t>
+          <t>33143</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103046</t>
+          <t>105098</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>143029</t>
+          <t>144899</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55834</t>
+          <t>55718</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85981</t>
+          <t>86321</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>169387</t>
+          <t>167099</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>217757</t>
+          <t>216466</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>181512</t>
+          <t>177196</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>223774</t>
+          <t>225450</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>104609</t>
+          <t>104598</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>139989</t>
+          <t>138773</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>300258</t>
+          <t>296883</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>355085</t>
+          <t>355037</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,54%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>110566</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149468</t>
+          <t>148987</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>90079</t>
+          <t>91524</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>122465</t>
+          <t>123915</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>208083</t>
+          <t>210680</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>260243</t>
+          <t>261691</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,57%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11433</t>
+          <t>11261</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3827</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16938</t>
+          <t>17307</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14184</t>
+          <t>15058</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34017</t>
+          <t>34500</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20323</t>
+          <t>20950</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24161</t>
+          <t>24812</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48851</t>
+          <t>48588</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87884</t>
+          <t>85487</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>121941</t>
+          <t>122091</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>81462</t>
+          <t>81843</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>114606</t>
+          <t>116818</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>178386</t>
+          <t>180140</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>226953</t>
+          <t>228005</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>142870</t>
+          <t>144857</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>182360</t>
+          <t>182881</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>130060</t>
+          <t>130699</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167812</t>
+          <t>168499</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>287035</t>
+          <t>284923</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>341008</t>
+          <t>337420</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>45,67%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59346</t>
+          <t>58740</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91397</t>
+          <t>90684</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90491</t>
+          <t>89754</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124794</t>
+          <t>126007</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>157750</t>
+          <t>156679</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>204908</t>
+          <t>205916</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18550</t>
+          <t>17599</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14368</t>
+          <t>14512</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10041</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26687</t>
+          <t>26696</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34892</t>
+          <t>34557</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62335</t>
+          <t>61018</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>988</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>9857</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38528</t>
+          <t>38301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65307</t>
+          <t>64895</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>127938</t>
+          <t>127996</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>169694</t>
+          <t>168927</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29267</t>
+          <t>30246</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51810</t>
+          <t>52107</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>165434</t>
+          <t>164577</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>211829</t>
+          <t>211427</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>188121</t>
+          <t>186736</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>233431</t>
+          <t>234873</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49422</t>
+          <t>49284</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73067</t>
+          <t>73723</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>244275</t>
+          <t>244089</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>295062</t>
+          <t>295791</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110259</t>
+          <t>108373</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>150156</t>
+          <t>147425</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43371</t>
+          <t>44263</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67992</t>
+          <t>69069</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>162214</t>
+          <t>163287</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>208408</t>
+          <t>210976</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,71%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20443</t>
+          <t>20039</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42102</t>
+          <t>40377</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,39 +2793,39 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>11797</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>6706</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>20160</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>1,65%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>11797</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>6718</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>20044</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,94%</t>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29353</t>
+          <t>30043</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54896</t>
+          <t>54395</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62481</t>
+          <t>62361</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>99472</t>
+          <t>96719</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26767</t>
+          <t>25904</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>50308</t>
+          <t>48880</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>97485</t>
+          <t>96224</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>138254</t>
+          <t>139297</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>294394</t>
+          <t>298576</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>359165</t>
+          <t>362380</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>136330</t>
+          <t>138343</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>180571</t>
+          <t>181767</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>448595</t>
+          <t>451555</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>522983</t>
+          <t>524138</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>499503</t>
+          <t>501192</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>569578</t>
+          <t>572949</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>279023</t>
+          <t>277683</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>330425</t>
+          <t>330168</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>795016</t>
+          <t>796209</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>885168</t>
+          <t>882056</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>236695</t>
+          <t>238277</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>296691</t>
+          <t>297883</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>180868</t>
+          <t>182703</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>227853</t>
+          <t>230233</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>429361</t>
+          <t>435871</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>504442</t>
+          <t>512796</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18990</t>
+          <t>19657</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17181</t>
+          <t>16933</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>29452</t>
+          <t>29998</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22678</t>
+          <t>23029</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15137</t>
+          <t>14716</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34532</t>
+          <t>34900</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41864</t>
+          <t>42366</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>71580</t>
+          <t>72058</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>83937</t>
+          <t>85172</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>120060</t>
+          <t>119695</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>112273</t>
+          <t>113284</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>154274</t>
+          <t>153933</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>210261</t>
+          <t>206934</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>261878</t>
+          <t>261147</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>131141</t>
+          <t>129475</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>170334</t>
+          <t>166439</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>238943</t>
+          <t>237807</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>288288</t>
+          <t>285758</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>381339</t>
+          <t>380231</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>440089</t>
+          <t>440413</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,96%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>44793</t>
+          <t>43591</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>72180</t>
+          <t>72441</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>121366</t>
+          <t>119087</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>163636</t>
+          <t>159983</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>173644</t>
+          <t>173769</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>223935</t>
+          <t>225241</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>23335</t>
+          <t>23456</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14341</t>
+          <t>13680</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>13541</t>
+          <t>15234</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>32063</t>
+          <t>34708</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>22556</t>
+          <t>22866</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>43428</t>
+          <t>43986</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>46879</t>
+          <t>47811</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>77269</t>
+          <t>78222</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>75722</t>
+          <t>75093</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>112962</t>
+          <t>112173</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>81613</t>
+          <t>82443</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>113933</t>
+          <t>113718</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>261037</t>
+          <t>263350</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>320342</t>
+          <t>324006</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>355961</t>
+          <t>357595</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>422446</t>
+          <t>423650</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>107447</t>
+          <t>107417</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>140955</t>
+          <t>139521</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>530891</t>
+          <t>529248</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>599208</t>
+          <t>596313</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>647789</t>
+          <t>648550</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>724517</t>
+          <t>725281</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,88%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>21866</t>
+          <t>22442</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>44428</t>
+          <t>45196</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>296712</t>
+          <t>294132</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>357273</t>
+          <t>355382</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>324465</t>
+          <t>324805</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>389847</t>
+          <t>391182</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>58165</t>
+          <t>55987</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>91993</t>
+          <t>91183</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>29997</t>
+          <t>31060</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>55276</t>
+          <t>58215</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>95105</t>
+          <t>94813</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>137702</t>
+          <t>137074</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>202300</t>
+          <t>199244</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>261085</t>
+          <t>256233</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,82 +4952,82 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>145484</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>124103</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>173749</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>373222</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>336481</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>411581</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
           <t>6,19%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>7,99%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>145484</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>124338</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>172156</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>373222</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>335677</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>413554</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>5,62%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>848648</t>
+          <t>851211</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>952196</t>
+          <t>959087</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>739305</t>
+          <t>737932</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>836190</t>
+          <t>837025</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1621046</t>
+          <t>1624163</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1759622</t>
+          <t>1760437</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1327232</t>
+          <t>1326496</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1441638</t>
+          <t>1443217</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1407284</t>
+          <t>1405475</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1514268</t>
+          <t>1519786</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2763458</t>
+          <t>2762825</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2920548</t>
+          <t>2921654</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,96%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>641010</t>
+          <t>640721</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>737085</t>
+          <t>731940</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>887395</t>
+          <t>889000</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>991698</t>
+          <t>990619</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1557709</t>
+          <t>1556289</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1693626</t>
+          <t>1695788</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15517</t>
+          <t>18462</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6559</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19352</t>
+          <t>18398</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23971</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>947</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7816</t>
+          <t>7830</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27012</t>
+          <t>28143</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61965</t>
+          <t>60868</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>96015</t>
+          <t>96723</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24080</t>
+          <t>23802</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47817</t>
+          <t>47353</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>92858</t>
+          <t>91310</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>133410</t>
+          <t>133305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>136134</t>
+          <t>134634</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>177934</t>
+          <t>177712</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87647</t>
+          <t>88207</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124019</t>
+          <t>123463</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>233384</t>
+          <t>233815</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>290158</t>
+          <t>289124</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,67%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160614</t>
+          <t>159354</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>203068</t>
+          <t>201228</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>149762</t>
+          <t>149833</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>187170</t>
+          <t>186240</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>320532</t>
+          <t>322096</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>376855</t>
+          <t>378764</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,66%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>848</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11239</t>
+          <t>11264</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13488</t>
+          <t>13688</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18565</t>
+          <t>19071</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,82 +6550,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>7069</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>15127</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>17803</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>10623</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>27511</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>7069</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2959</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>14401</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>17803</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>10850</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>27357</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73705</t>
+          <t>74232</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109195</t>
+          <t>110103</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45566</t>
+          <t>47647</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76140</t>
+          <t>77662</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>127729</t>
+          <t>127227</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>176123</t>
+          <t>175148</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>143515</t>
+          <t>140649</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>185474</t>
+          <t>183391</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80398</t>
+          <t>80939</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115307</t>
+          <t>113946</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>231505</t>
+          <t>230891</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>288816</t>
+          <t>287261</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>130480</t>
+          <t>130918</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>172539</t>
+          <t>172388</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>148036</t>
+          <t>146906</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>187685</t>
+          <t>186473</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>290473</t>
+          <t>290534</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>347615</t>
+          <t>348018</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,22%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12377</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13191</t>
+          <t>13238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14759</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34097</t>
+          <t>34802</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20451</t>
+          <t>19635</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23766</t>
+          <t>23984</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47590</t>
+          <t>48703</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>112802</t>
+          <t>113170</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>155867</t>
+          <t>155283</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26338</t>
+          <t>26550</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50584</t>
+          <t>49712</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>146946</t>
+          <t>146850</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>194848</t>
+          <t>196698</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>207841</t>
+          <t>205900</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>257685</t>
+          <t>256784</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66082</t>
+          <t>64916</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96389</t>
+          <t>95380</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>282434</t>
+          <t>283429</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>341143</t>
+          <t>342478</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,5%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213116</t>
+          <t>213795</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261882</t>
+          <t>260802</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>113540</t>
+          <t>112965</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>146820</t>
+          <t>147897</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>336150</t>
+          <t>334611</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>396019</t>
+          <t>393631</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,25%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11211</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29582</t>
+          <t>28629</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>17533</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19280</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40453</t>
+          <t>40355</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>34435</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63465</t>
+          <t>62606</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15743</t>
+          <t>14743</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37687</t>
+          <t>37532</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>54844</t>
+          <t>56326</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>89145</t>
+          <t>91017</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>241754</t>
+          <t>241298</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>301277</t>
+          <t>301183</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>109708</t>
+          <t>110218</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>156604</t>
+          <t>155119</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>364648</t>
+          <t>367730</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>438035</t>
+          <t>441882</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>372527</t>
+          <t>374693</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>441313</t>
+          <t>440118</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>230427</t>
+          <t>232001</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>287187</t>
+          <t>287329</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>624520</t>
+          <t>622622</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>711378</t>
+          <t>711465</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>378961</t>
+          <t>377298</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>446606</t>
+          <t>445577</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>310703</t>
+          <t>307931</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>369431</t>
+          <t>367077</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>704470</t>
+          <t>703990</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>795993</t>
+          <t>793279</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,34%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17497</t>
+          <t>17922</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15455</t>
+          <t>16239</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11149</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>27374</t>
+          <t>27861</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17051</t>
+          <t>16840</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>36999</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>15394</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>35004</t>
+          <t>34323</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>36341</t>
+          <t>36614</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>64435</t>
+          <t>65817</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>96203</t>
+          <t>95617</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>134287</t>
+          <t>132950</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>109227</t>
+          <t>109636</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>152338</t>
+          <t>151871</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>218559</t>
+          <t>219486</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>274580</t>
+          <t>277457</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>147766</t>
+          <t>146754</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>189989</t>
+          <t>191497</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>223345</t>
+          <t>222530</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>275032</t>
+          <t>277754</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>383766</t>
+          <t>383053</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>450282</t>
+          <t>453194</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,69%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>169624</t>
+          <t>168428</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>214880</t>
+          <t>213499</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>321615</t>
+          <t>322998</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>380281</t>
+          <t>380369</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>503575</t>
+          <t>502673</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>574278</t>
+          <t>575490</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,32%</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>20758</t>
+          <t>20065</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21301</t>
+          <t>20615</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>16112</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>36382</t>
+          <t>36120</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>18201</t>
+          <t>18851</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>24112</t>
+          <t>23985</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>48922</t>
+          <t>48453</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>47241</t>
+          <t>48892</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>79843</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>77466</t>
+          <t>78967</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>108874</t>
+          <t>110107</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>163386</t>
+          <t>165366</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>216770</t>
+          <t>215356</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>251717</t>
+          <t>253382</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>311238</t>
+          <t>311270</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>63304</t>
+          <t>64700</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>93020</t>
+          <t>94399</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>356512</t>
+          <t>358059</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>424080</t>
+          <t>423318</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>434637</t>
+          <t>436150</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>502080</t>
+          <t>505869</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,76%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>43322</t>
+          <t>42553</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>70597</t>
+          <t>72259</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>450439</t>
+          <t>451994</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>519043</t>
+          <t>516585</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>504050</t>
+          <t>502058</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>575539</t>
+          <t>577967</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>42,0%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>42147</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>72327</t>
+          <t>72540</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>25179</t>
+          <t>25508</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>50096</t>
+          <t>50105</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>74974</t>
+          <t>75625</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>114150</t>
+          <t>113123</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>124683</t>
+          <t>125860</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>173559</t>
+          <t>171553</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>85424</t>
+          <t>85335</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>127048</t>
+          <t>126037</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>222452</t>
+          <t>221072</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>283706</t>
+          <t>285296</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>730206</t>
+          <t>728500</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>832877</t>
+          <t>834169</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>541235</t>
+          <t>539529</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>626707</t>
+          <t>628933</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1297076</t>
+          <t>1296629</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1434294</t>
+          <t>1436346</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1150584</t>
+          <t>1144401</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1261568</t>
+          <t>1259832</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1127615</t>
+          <t>1122405</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1241456</t>
+          <t>1236930</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2302222</t>
+          <t>2301543</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2469359</t>
+          <t>2466361</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1172304</t>
+          <t>1171898</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1283491</t>
+          <t>1287251</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1571191</t>
+          <t>1575517</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1694108</t>
+          <t>1704405</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2778916</t>
+          <t>2778334</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2947352</t>
+          <t>2947394</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>7542</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10768,7 +10768,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8502</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23619</t>
+          <t>21080</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15252</t>
+          <t>15636</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31212</t>
+          <t>31048</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62178</t>
+          <t>61171</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>96720</t>
+          <t>94033</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39264</t>
+          <t>38353</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65241</t>
+          <t>65103</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>109939</t>
+          <t>108006</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>152828</t>
+          <t>151846</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>164931</t>
+          <t>163911</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>208982</t>
+          <t>206032</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125011</t>
+          <t>125501</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>162061</t>
+          <t>162232</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>300314</t>
+          <t>304632</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>358010</t>
+          <t>359878</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,43%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>133661</t>
+          <t>133219</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>176665</t>
+          <t>174174</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>122536</t>
+          <t>121788</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>158411</t>
+          <t>159722</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>265955</t>
+          <t>263367</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>322154</t>
+          <t>319874</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,27%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>998</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9885</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6872</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12815</t>
+          <t>12664</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23178</t>
+          <t>21338</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16955</t>
+          <t>17908</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14341</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33254</t>
+          <t>34589</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49740</t>
+          <t>51209</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>80245</t>
+          <t>82274</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50579</t>
+          <t>52234</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>80376</t>
+          <t>82105</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>109510</t>
+          <t>107533</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>150018</t>
+          <t>149380</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>160839</t>
+          <t>158223</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>200692</t>
+          <t>201001</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>138973</t>
+          <t>137949</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>175356</t>
+          <t>178150</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>310632</t>
+          <t>313200</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>367381</t>
+          <t>367080</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,34%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97778</t>
+          <t>96792</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135042</t>
+          <t>133620</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114574</t>
+          <t>113448</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>151271</t>
+          <t>151863</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>225103</t>
+          <t>219500</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>274964</t>
+          <t>274634</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,91%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15122</t>
+          <t>15156</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,82 +12127,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6759</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>10250</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>5131</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>19446</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,75%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1930</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6481</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>10250</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>5182</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>18485</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18065</t>
+          <t>17225</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39318</t>
+          <t>38760</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>18756</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41177</t>
+          <t>40124</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>102482</t>
+          <t>101638</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>144618</t>
+          <t>139533</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19376</t>
+          <t>20855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40488</t>
+          <t>40837</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>128362</t>
+          <t>129097</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>172777</t>
+          <t>172498</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>206437</t>
+          <t>208859</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>254003</t>
+          <t>254047</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58294</t>
+          <t>56670</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84219</t>
+          <t>84830</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>276396</t>
+          <t>275530</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>331384</t>
+          <t>329069</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>115762</t>
+          <t>113486</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156242</t>
+          <t>152997</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48374</t>
+          <t>48527</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73895</t>
+          <t>75641</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>170069</t>
+          <t>170862</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216802</t>
+          <t>217001</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13726</t>
+          <t>13745</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21434</t>
+          <t>21194</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>12502</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28571</t>
+          <t>30426</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>35670</t>
+          <t>36684</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63836</t>
+          <t>62491</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9667</t>
+          <t>8960</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26488</t>
+          <t>25404</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>50456</t>
+          <t>49604</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>82240</t>
+          <t>81161</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>246294</t>
+          <t>247360</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>304122</t>
+          <t>303721</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>146974</t>
+          <t>147592</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>193897</t>
+          <t>195646</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>409768</t>
+          <t>407207</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>487055</t>
+          <t>481693</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>480873</t>
+          <t>480675</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>547325</t>
+          <t>548083</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>315422</t>
+          <t>313933</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>373140</t>
+          <t>371152</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>809109</t>
+          <t>813928</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>903426</t>
+          <t>904075</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,07%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>267195</t>
+          <t>264252</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>324674</t>
+          <t>324511</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>253276</t>
+          <t>251234</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>308256</t>
+          <t>311664</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>537561</t>
+          <t>536591</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>619298</t>
+          <t>614855</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16665</t>
+          <t>17418</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16253</t>
+          <t>16319</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>29617</t>
+          <t>28615</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14166</t>
+          <t>14676</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>32817</t>
+          <t>33540</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26930</t>
+          <t>26746</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27310</t>
+          <t>28282</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>50777</t>
+          <t>52795</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>117684</t>
+          <t>115339</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>160659</t>
+          <t>158532</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>115974</t>
+          <t>115256</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>158524</t>
+          <t>162811</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>247192</t>
+          <t>243284</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>306308</t>
+          <t>301491</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>258159</t>
+          <t>256376</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>308468</t>
+          <t>309250</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>295223</t>
+          <t>295926</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>346937</t>
+          <t>349481</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>567816</t>
+          <t>568385</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>641565</t>
+          <t>640946</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,38%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>141870</t>
+          <t>144851</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>188941</t>
+          <t>188390</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,47 +13943,47 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>30,55%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>252724</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>225557</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>278684</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>34,33%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
           <t>30,64%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>252724</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>224761</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>278731</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>34,33%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>30,53%</t>
-        </is>
-      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>384413</t>
+          <t>381130</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>453761</t>
+          <t>451712</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14819</t>
+          <t>14828</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,7 +14173,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>7841</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25096</t>
+          <t>25803</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14585</t>
+          <t>14318</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>35046</t>
+          <t>35431</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>25866</t>
+          <t>25515</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>26128</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>51438</t>
+          <t>50990</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>41272</t>
+          <t>40150</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>69862</t>
+          <t>69828</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,7 +14356,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>66147</t>
+          <t>70245</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>98718</t>
+          <t>100132</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>182144</t>
+          <t>184425</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>236144</t>
+          <t>238274</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>263279</t>
+          <t>263478</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>323944</t>
+          <t>324309</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>92287</t>
+          <t>92367</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>125679</t>
+          <t>124680</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>404562</t>
+          <t>405144</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>471916</t>
+          <t>471280</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>509688</t>
+          <t>508543</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>585764</t>
+          <t>581699</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>55913</t>
+          <t>55359</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>85086</t>
+          <t>87631</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>343924</t>
+          <t>341279</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>411232</t>
+          <t>407183</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>413289</t>
+          <t>413695</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>480976</t>
+          <t>483789</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,53%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>27484</t>
+          <t>26782</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>52234</t>
+          <t>51616</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>31574</t>
+          <t>31376</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>58932</t>
+          <t>57375</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>62957</t>
+          <t>65668</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>98917</t>
+          <t>102856</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>116245</t>
+          <t>113852</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>164106</t>
+          <t>159553</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>73274</t>
+          <t>71535</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>110951</t>
+          <t>109564</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>196844</t>
+          <t>199036</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>258944</t>
+          <t>259927</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>705595</t>
+          <t>708717</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>807521</t>
+          <t>807885</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>613329</t>
+          <t>612733</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>709315</t>
+          <t>704464</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1354471</t>
+          <t>1347216</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1488382</t>
+          <t>1483043</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1449445</t>
+          <t>1447029</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1561123</t>
+          <t>1564094</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1416808</t>
+          <t>1412510</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1537844</t>
+          <t>1537031</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2894697</t>
+          <t>2894625</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3065764</t>
+          <t>3063875</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,51%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>878832</t>
+          <t>880706</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>984555</t>
+          <t>990297</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1188117</t>
+          <t>1183993</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1305355</t>
+          <t>1301283</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2092005</t>
+          <t>2093678</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2253460</t>
+          <t>2250369</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
